--- a/output/第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx
+++ b/output/第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx
@@ -43,6 +43,11 @@
     </font>
     <font>
       <name val="游ゴシック"/>
+      <i val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="10"/>
@@ -52,11 +57,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <i val="1"/>
-      <sz val="8.5"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -83,17 +83,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="005B9BD5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,14 +133,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,22 +152,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,7 +188,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -556,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -580,281 +583,293 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="168" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>【本表の時点について】
+本表は令和8年8月31日のご指示に対する検討の資料であり、その時点での案Cの組立てを示すものです。その後、案Cの組立ては次のとおり改めました。最新の案Cは別冊「将来推計（人口と認定者数）」及び「サービス見込量の算定」によります。
+・水準の起点　本表は令和7年国勢調査人口速報集計（3町計27,651人）を総人口の起点とし、令和11年度の総人口を26,995人としています。最新の案Cは、地域包括ケア「見える化」システムのA系列（社人研推計）の令和7年の値27,102人を総人口の起点とし、令和11年度の総人口を26,460人としています（見える化システムへ入力する総人口の設定と同じ系列にそろえるため）。両者の差549人は、国勢調査の実績と社人研推計の差です。
+・階級別人口の起点　本表は住民基本台帳の令和7年1月1日現在、最新の案Cは介護保険事業状況報告の令和8年3月末現在の第1号被保険者数（実績）を起点としています。
+・認定率　本表は階級別認定率を令和8年3月末で固定するシナリオ①により令和11年度の認定者数を2,108人としています。最新の案Cはシナリオ②（トレンド継続）により2,067人です。
+・階級別人口の表示　本表は階級別を丸めたうえで掲げているため、内訳の和（令和11年度 9,213人）と「計」の欄（9,212人）が1人違います。計の欄は丸める前の和を丸めたものです。公表する表では内訳の和と計を一致させます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>【1　ご指示をそのまま実行するにあたっての制約】</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>制約</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>受託者の対応</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>程度</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="5" t="n">
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>総合戦略の目標人口は総人口のみである</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>3町の第3期まち・ひと・しごと創生総合戦略が示すのは総人口の目標値です。介護保険の推計に必要なのは年齢階級別の人口（65〜74歳・75〜84歳・85歳以上）であり、総合戦略からは得られません。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>年齢階級別は住民基本台帳の実績趨勢（平成31年〜令和7年の7年分）を用います。社人研の伸び率は用いません。</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="5" t="n">
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>美瑛町は目標が設定されていない</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>第3期総合戦略に人口の目標値がありません。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>美瑛町の総人口は住民基本台帳の実績趨勢により延長します。総合戦略の値をお持ちであればご提供をお願いします。</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="5" t="n">
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>東神楽町の目標は実績から離れつつある</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>目標は「9,500人維持（令和11年度）」ですが、令和7年国勢調査（速報）は9,588人で、令和8年中に9,500人を割り込む見込みです。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>目標値をそのまま用いると過大になります。目標値を用いるか実績の趨勢を用いるかのご判断をお願いします。</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="5" t="n">
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>東川町の目標は実績が既に上回っている</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>目標は「8,635人（令和11年度）」ですが、令和7年国勢調査（速報）は8,726人で、既に91人上回っています。</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>目標値をそのまま用いると過小になります。同上。</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="5" t="n">
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>基準時点が町により異なる</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>総合戦略の基準時点は町により異なります。</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>令和7年国勢調査（人口速報集計）を3町共通の基準に揃えます。</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>【2　受託者の対応方針】</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>事項</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>根拠</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>案Cを組み立てた</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>総人口は総合戦略の目標（東川町・東神楽町）と住民基本台帳の実績趨勢（美瑛町）により、年齢階級別は住民基本台帳の実績趨勢により推計しました。社人研の伸び率は用いていません。</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>総合戦略、住民基本台帳（平成31年〜令和7年）、令和7年国勢調査</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>3案を並べて比較した</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>A 社人研（現行の推計）、B 社人研＋補正（現行の受託者案）、C 総合戦略・住民基本台帳の実績趨勢の3案です。</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>04シート・05シート</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>保険料への影響を算定した</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>指数による概算では、令和11年度の月額基準額は案A 6,670円・案B 6,578円・案C 6,774円です。第1段階から第3段階まで通して再計算した案Cは6,740円です。</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>将来推計 第3段階の基本ケースは案Cに置き換えました</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>成果品の書き換えは着手していない</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>採用案が決まるまで、既存の成果品（将来推計 第1〜3段階、計画素案、図表集）は現行のまま（案A・案B）としています。採用案の決定後に一括して置き換えます。</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>01シートに書き換えの対象を掲げています</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>注1）「総合戦略上の人口で推計する」というご指示を文字どおり実行することはできません。総合戦略が示すのは総人口の目標のみであり、美瑛町には目標がなく、年齢階級別の内訳もないためです。
 注2）案Cは、ご指示の趣旨（社人研の推計をそのまま用いない）を実行できる形にしたものです。社人研の伸び率を用いず、住民基本台帳の実績趨勢によります。
@@ -863,12 +878,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -906,399 +922,399 @@
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>成果品・箇所</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>用いている系列</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>用い方</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>案C採用時の扱い</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>将来推計 第1段階 01_人口の前提</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>見える化A2・A3・A4（社人研）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>総人口・65歳以上・前期後期の推移を掲げている</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>案Cの値に差し替える。社人研は参考として残す</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>将来推計 第1段階 02_推計上の階級別人口</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>見える化A4の階級別の伸び率</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>実績人口（令和8年3月末）に社人研の伸び率を乗じている。推計の中核である</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>住民基本台帳の実績趨勢の伸び率に差し替える</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>将来推計 第1段階 03_認定者数の推計</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>同上（02シートの人口を受ける）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>階級別人口×階級別認定率</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>02シートの差替えにより自動的に変わる</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>人口推計の補正（8シート）</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>見える化A2・A3、社人研 結果表3</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>社人研の伸び率を住民基本台帳の実績で補正する表である</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>案Cでは補正そのものが不要になる。案A・案Bとの対比の資料として残す</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>将来推計 第2段階 サービス見込量</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>第1段階の認定者数</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>認定者数×区分別利用率×1人当たり日数回数</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>第1段階の差替えにより自動的に変わる</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>将来推計 第3段階 給付費と保険料</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>見える化の自然体推計（社人研ベース）、推計上の第1号被保険者数</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>標準給付費見込額と補正後被保険者数の分母に用いている</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>認定者数と第1号被保険者数の差替えにより変わる。05シートに影響を示した</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>計画素案 第2章第1節</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>見える化A系列</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>人口推計の基礎と第9期計画との差の説明</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>案Cの説明に書き換える。［要協議］を外す</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>計画素案 第6章第1〜3節・第6節</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>第1〜3段階の結果</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>認定者数の見込み・見込量・給付費・保険料</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>差替え</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>計画素案 第2章第8節 中長期推計</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>見える化A系列（令和22年・令和32年）</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>2040年・2050年の需要と財政の見通し</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>総合戦略は令和11年度までのため、中長期は社人研によらざるを得ない。基礎が異なる旨を注記する</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>図表集 01_人口推移・16_町別将来推計・17_担い手の推移</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>見える化A系列</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>図1・図15・図16</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>案Cの値で作図し直す</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>3町ヒアリング資料 第3節</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>社人研 vs 住民基本台帳</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>補正の考え方の説明</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>案Cの説明に書き換える</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>地域差の分析・世帯構成の突合ほか</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>見える化A系列（水準の参照）</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>高齢化率等を参照しているのみで推計には用いていない</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>そのまま。出典の表記のみ確認する</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>注1）「大」は推計値そのものが変わるもの、「中」は表示が変わるもの、「小」は出典の表記のみのものです。
 注2）中長期推計（令和22年・令和32年）は、総合戦略が令和11年度までしか目標を持たないため、社人研によらざるを得ません。第10期の3年間と中長期とで基礎が異なることを本文に明記します。
@@ -1348,239 +1364,239 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>【1　目標と実績】</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>総合戦略の目標</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>令和7年
 国勢調査</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>目標との差</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>案Cで用いる
 令和11年度</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>扱いと理由</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>東川町</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>8,635人（令和11年度）</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>8726</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>8635</v>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>実績が既に目標を91人上回っています。目標をそのまま用いると過小になります</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>設定なし</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>9337</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>8860</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>目標が設定されていないため、令和7年国勢調査を起点に住民基本台帳の実績趨勢（年-1.30％）で延長しました。総合戦略の値をお持ちであればご提供をお願いします</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>東神楽町</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>9,500人維持（令和11年度）</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>9588</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>9500</v>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>令和8年中に目標を割り込む見込みです。目標をそのまま用いると過大になります</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>27651</v>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <v>26995</v>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>案Cの令和11年度の総人口です</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>【2　社人研の推計との対比（令和11年度の総人口）】</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>総人口</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>案Cとの差</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>率</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>案C（総合戦略・住基趨勢）</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="12" t="n">
         <v>26995</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>+0.0％</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>本表の推計</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>案A・案B（社人研）</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>26195</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>-800</v>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>-3.0％</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>見える化A2（社人研 令和5年推計）の令和11年度</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>注1）総合戦略の目標は総人口のみです。年齢階級別の内訳はありません。
 注2）案Cの総人口は、東川町と東神楽町は総合戦略の目標値、美瑛町は令和7年国勢調査を起点とした住民基本台帳の実績趨勢です。3町計は社人研の推計を+800人（+3.1％）上回ります。
@@ -1633,445 +1649,445 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>【1　住民基本台帳の実績と年平均変化率（3町計）】</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>平成31年</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>令和7年</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>6年の増減</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>年平均変化率</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>所見</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>総人口</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>28746</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>27731</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>-1015</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>-0.597％</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>総人口は減る</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>4211</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>3817</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>-394</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>-1.624％</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>団塊世代が75歳以上へ移行するため減る</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>75〜84歳</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>3192</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>3455</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>+1.328％</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>団塊世代の移行により増える</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>85歳以上</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>1743</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>1960</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>+1.975％</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>一貫して増える。認定者数の増加はここが源である</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>【2　案Cの階級別人口（3町計・人）】</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>令和7年度
 （実績）</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>令和7→11年度</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="12" t="n">
         <v>3600</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>3542</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>3484</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>3427</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>3372</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="12" t="n">
         <v>-228</v>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>75〜84歳</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>3499</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>3545</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>3593</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>3640</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>3689</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="12" t="n">
         <v>190</v>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>85歳以上</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>1990</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>2029</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>2069</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>2110</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>2152</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <v>162</v>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>65歳以上　計</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="16" t="n">
         <v>9089</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>9116</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>9146</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="16" t="n">
         <v>9178</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="16" t="n">
         <v>9212</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="16" t="n">
         <v>123</v>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>第1号被保険者数となる</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">　うち75歳以上</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
         <v>5489</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>5575</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>5662</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>5751</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <v>5841</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <v>352</v>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>【3　案Cの認定者数（3町計・人）】</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>令和7年度
 （実績）</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>令和7→11年度</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>認定者数</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="16" t="n">
         <v>1984</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>2014</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>2045</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="16" t="n">
         <v>2076</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="16" t="n">
         <v>2108</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="16" t="n">
         <v>124</v>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>階級別認定率は令和8年3月末で固定</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>認定率</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>21.83％</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>22.09％</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>22.35％</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>22.62％</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>22.88％</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="68" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>注1）階級別認定率は令和8年3月末の値（65〜74歳4.03％・75〜84歳17.52％・85歳以上61.60％）で固定しています（シナリオ①現状固定）。認定率のシナリオの選択は人口の基礎とは別の論点です。
 注2）水準の起点は令和7年度末（令和8年3月末）の実績人口です。住民基本台帳の水準（令和7年1月1日9,232人）ではなく、介護保険事業状況報告の第1号被保険者数（9,090人）に合わせています。住民基本台帳から取るのは伸び率のみです。
@@ -2125,469 +2141,469 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>【1　令和11年度の比較】</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>案A
 社人研</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>案B
 社人研＋補正</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>案C
 総合戦略・住基趨勢</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>C－A</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>C－B</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>所見</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>3403</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>3531</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>3372</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>-31</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>-160</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>案Cは案Aを下回る。住民基本台帳の減少が社人研より速い</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>75〜84歳</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>3597</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>3571</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>3689</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>85歳以上</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>2072</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>2057</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>2152</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>案Cが最も多い。認定率61.6％の層である</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>65歳以上　計</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>9072</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>9159</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>9212</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <v>140</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="16" t="n">
         <v>53</v>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>第1号被保険者数。保険料の分母となる</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">　うち75歳以上</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>5669</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>5628</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>5841</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>213</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>案Cは案Aを172人上回る</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>認定者数</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>2044</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>2035</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>2108</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <v>64</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="16" t="n">
         <v>73</v>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>案Cが最も多い。85歳以上が多いため</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>認定率</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>22.53％</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>22.22％</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>22.88％</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>階級別認定率は3案とも同じ。差は年齢構成による</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>【2　年度別の推移（65歳以上・人）】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>案</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>令和7年度
 （実績）</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>A 社人研（現行の推計）</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>9089</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>9086</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>9081</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>9078</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>9072</v>
       </c>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>B 社人研＋補正（現行の受託者案）</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
         <v>9089</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>9179</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>9172</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>9167</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <v>9159</v>
       </c>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>C 総合戦略・住民基本台帳の実績趨勢</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
         <v>9089</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <v>9116</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <v>9146</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="12" t="n">
         <v>9178</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="12" t="n">
         <v>9212</v>
       </c>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>【3　年度別の推移（認定者数・人）】</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>案</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>令和7年度
 （実績）</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>A 社人研（現行の推計）</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="12" t="n">
         <v>1984</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="12" t="n">
         <v>1999</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="12" t="n">
         <v>2014</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>2029</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>2044</v>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>B 社人研＋補正（現行の受託者案）</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="12" t="n">
         <v>1984</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <v>1991</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>2006</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="12" t="n">
         <v>2021</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="12" t="n">
         <v>2035</v>
       </c>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>C 総合戦略・住民基本台帳の実績趨勢</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="12" t="n">
         <v>1984</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="12" t="n">
         <v>2014</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="12" t="n">
         <v>2045</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>2076</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="12" t="n">
         <v>2108</v>
       </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>注1）3案とも、令和7年度末の実績人口を起点とし、伸び率のみを変えています。案Aは社人研、案Bは社人研に住民基本台帳による補正を加えたもの、案Cは住民基本台帳の実績趨勢です。
 注2）階級別認定率は3案とも令和8年3月末で固定しています。認定者数の差は年齢構成の差によるものです。
@@ -2640,459 +2656,459 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>【1　月額基準額の比較】</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>案</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>認定者数
 （指数）</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>第1号被保険者数
 （指数）</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>保険料の指数</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>月額基準額</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>A 社人研（現行の推計）</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>6,670円</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>現行の推計（将来推計 第3段階の基本ケース）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>B 社人研＋補正（現行の受託者案）</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>0.9957</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>1.0096</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.9863</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>6,578円</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>現行の受託者案（人口推計の補正 案B）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>C 総合戦略・住民基本台帳の実績趨勢</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>1.0313</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>1.0155</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>1.0156</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>6,774円</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>本表の案。ご指示に沿ったもの</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>【2　案の間の差】</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>比較</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>差（月額）</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>率</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>案C －案A</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>+104円</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>+1.6％</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>社人研をそのまま用いる場合との差</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>案C －案B</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>+196円</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>+2.9％</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>現行の受託者案との差。基礎の選び方で保険料がこれだけ動く</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>案B －案A</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>-92円</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>-1.4％</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>補正の効果</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>【3　この試算の前提】</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>前提</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>留意</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>給付費は認定者数に比例する</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>認定者数の指数をそのまま給付費の指数としています。</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>実際には75歳以上の増は重度者の増であり、1人当たり給付費の高い層が増えます。案Cの給付費は本試算より大きくなる可能性があります</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>サービスの構成は変えていない</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>要介護度別・サービス種別の構成は3案とも同じとしています。</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>第2段階（サービス見込量）の再計算により精緻化できます</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>補正後被保険者数は被保険者数に比例する</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>所得段階別加入割合補正後の被保険者数は、第1号被保険者数に比例するとしています。</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>所得段階の分布が変わらないという仮定です</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>他の前提は基本ケースと同じ</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>標準給付費見込額への割増率、地域支援事業費、第1号被保険者負担割合、調整交付金、収納率、基金取崩額は将来推計 第3段階の基本ケースと同じです。</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>【4　通し再計算の結果（令和8年8月31日）】</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>月額基準額</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>第9期条例
 との差</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>従前（案A）</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>6,670円</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>+270円</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>社人研を基礎としていたときの基本ケース</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>概算（案C）</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>6,774円</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>+374円</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>本シート【1】の指数による概算</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>通し再計算（案C）</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>6,740円</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>+340円</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>将来推計 第1段階から第3段階まで通して再計算した値。第3段階 01シート・05シートによる。本表で採る値</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>通し再計算では、認定者数の比（3年計1.0233倍）を見える化システムの自然体推計による給付費に乗じ、第1号被保険者数を案Cの値（3年計27,539人）に置き換えています。概算との差-34円は、年度別の比を用いたことと、被保険者数を四捨五入したことによるものです。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="68" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>注1）【1】〜【3】は概算です。【4】に第1段階から第3段階まで通して再計算した値を示しました。
 注2）案Cは案Bより月額+196円です。人口の基礎の選び方で保険料が約200円動きます。第9期の条例基準額6,400円との比較では、案Bが＋192円、案Cが＋388円です。
@@ -3147,279 +3163,279 @@
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>事項</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>受託者の案</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>決定の時期</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>どの案を採るか</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>A 社人研、B 社人研＋補正、C 総合戦略・住民基本台帳の実績趨勢。概算による令和11年度の月額基準額は6,670円・6,578円・6,774円、通し再計算による案Cは6,740円です。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>ご指示の趣旨に沿うのは案Cです。ただし案Cは総合戦略の目標を3町一律には用いられません。</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>美瑛町の総合戦略の人口目標</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>第3期総合戦略に人口の目標値がありません。人口ビジョン等に推計値があればご提供をお願いします。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>得られない場合は住民基本台帳の実績趨勢で延長します（本表の案C）。</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>東川町・東神楽町の目標値の扱い</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>東川町は実績が目標を91人上回り、東神楽町は令和8年中に目標を割り込む見込みです。目標値をそのまま用いるか、実績の趨勢を用いるか。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>総人口は目標値、年齢階級別は実績趨勢とする（本表の案C）。総人口は保険料に直接効かないためです。</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>年齢階級別の内訳の作り方</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>総合戦略には年齢階級別の内訳がありません。住民基本台帳の実績趨勢によるか、社人研の構成比によるか。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>住民基本台帳の実績趨勢によります（本表の案C）。社人研を用いないというご指示に沿うためです。</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>中長期推計（令和22年・令和32年）の扱い</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>総合戦略は令和11年度までしか目標を持ちません。2040年・2050年の見通しは社人研によらざるを得ません。</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>中長期は社人研によることとし、第10期の3年間と基礎が異なる旨を本文に明記します。</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>認定率のシナリオ</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>①現状固定、②トレンド継続、③令和元年水準へ回帰。人口の基礎とは別の論点です。</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>②トレンド継続（従来からの受託者案）。本表は比較のため①現状固定で揃えています。</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>令和8年10月</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>住民基本台帳の期間</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>本表は平成31年から令和7年までの6年で年平均変化率を算定しています。期間の取り方で伸び率が変わります。</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>6年（入手済みの全期間）を用います。3年・5年で算定した場合の感度は決定後にお示しします。</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>令和7年国勢調査の確報値</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>本表は人口速報集計によっています。人口等基本集計（令和8年11月頃公表見込み）で年齢構成が確定します。</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>確報の公表後に差し替えます。</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>令和8年11月</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="14" ht="68" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>注1）採用案が決まるまで、既存の成果品は現行のまま（案A・案B）としています。決定前に書き換えると、決定が変わった場合に二重の手戻りが生じるためです。
 注2）決定後の書き換えは、将来推計 第1〜3段階、計画素案、図表集、3町ヒアリング資料が対象です（01シート）。所要は1週間程度を見込んでいます。
